--- a/data/trans_orig/P32C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2007 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1935</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12065</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5733</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2869</t>
+          <t>1974</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14496</t>
+          <t>13778</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>134084</t>
+          <t>132820</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144262</t>
+          <t>144214</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>67743</t>
+          <t>69421</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205129</t>
+          <t>205847</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>216756</t>
+          <t>217651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,4%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>99,1%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2005</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12349</t>
+          <t>12350</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2833</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12706</t>
+          <t>12961</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,3%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216468</t>
+          <t>216467</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226812</t>
+          <t>226694</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>72751</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288862</t>
+          <t>288607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>299539</t>
+          <t>298735</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,06%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4755</t>
+          <t>5464</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,62 +1454,62 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5232</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>939</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4061</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>189185</t>
+          <t>188476</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85097</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86969</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>276848</t>
+          <t>275677</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,14%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>1977</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12791</t>
+          <t>13776</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8519</t>
+          <t>7164</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2463</t>
+          <t>2972</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>15533</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>225104</t>
+          <t>224119</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235922</t>
+          <t>235918</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122407</t>
+          <t>123762</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,49%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>354002</t>
+          <t>353289</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>366359</t>
+          <t>365850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4301</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8540</t>
+          <t>7910</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9440</t>
+          <t>9488</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92387</t>
+          <t>92597</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38756</t>
+          <t>39386</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134754</t>
+          <t>134706</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6577</t>
+          <t>6047</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>876</t>
+          <t>881</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>7958</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>187707</t>
+          <t>188237</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,61%</t>
+          <t>96,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106864</t>
+          <t>106624</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>297703</t>
+          <t>298109</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305191</t>
+          <t>305186</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3303</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14075</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>1924</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2743</t>
+          <t>3345</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14159</t>
+          <t>14364</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>274972</t>
+          <t>274772</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>286175</t>
+          <t>285744</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,86%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>129521</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>131445</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406333</t>
+          <t>406128</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>417749</t>
+          <t>417147</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,2%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3304</t>
+          <t>3282</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>13348</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>998</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>8261</t>
+          <t>7950</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5406</t>
+          <t>4722</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17647</t>
+          <t>17674</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>479112</t>
+          <t>479540</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>489584</t>
+          <t>489606</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,7 +3262,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,21%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>231677</t>
+          <t>231988</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>238940</t>
+          <t>239938</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,58%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>715179</t>
+          <t>715152</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>727420</t>
+          <t>728104</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>24534</t>
+          <t>25161</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49733</t>
+          <t>49639</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3529</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>16377</t>
+          <t>17009</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31280</t>
+          <t>31509</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>59731</t>
+          <t>57626</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,08%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1830185</t>
+          <t>1830279</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1855384</t>
+          <t>1854757</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,69%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>878207</t>
+          <t>877575</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>891055</t>
+          <t>891114</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,7 +3640,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2714772</t>
+          <t>2716877</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2743223</t>
+          <t>2742994</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2012 (tasa de respuesta: 99,17%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>6260</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20629</t>
+          <t>19905</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5990</t>
+          <t>6012</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7198</t>
+          <t>6857</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22060</t>
+          <t>21280</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>154696</t>
+          <t>155420</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169307</t>
+          <t>169065</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103702</t>
+          <t>103680</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>262957</t>
+          <t>263737</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>277819</t>
+          <t>278160</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,47%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10998</t>
+          <t>11378</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2076</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1736</t>
+          <t>1805</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11726</t>
+          <t>11099</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>298228</t>
+          <t>297848</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307349</t>
+          <t>307440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>147296</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>149372</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>446872</t>
+          <t>447499</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456862</t>
+          <t>456793</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,61%</t>
         </is>
       </c>
     </row>
@@ -4742,97 +4742,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1894</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,95%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2075</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>197508</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>199402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>119176</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121251</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>318687</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>320653</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>99,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>1026</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9344</t>
+          <t>9246</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1031</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9469</t>
+          <t>9955</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177461</t>
+          <t>177559</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185778</t>
+          <t>185779</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>85350</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>87342</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264678</t>
+          <t>264192</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273116</t>
+          <t>273143</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>892</t>
+          <t>914</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>8799</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>8477</t>
+          <t>9797</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>120141</t>
+          <t>119409</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127316</t>
+          <t>127294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>54109</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>173840</t>
+          <t>172520</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181408</t>
+          <t>181403</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5341</t>
+          <t>5345</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,62 +5806,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1054</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1962</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5355</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1054</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5337</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179865</t>
+          <t>179861</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>97,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92244</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>94206</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274075</t>
+          <t>274057</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4371</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>15303</t>
+          <t>16824</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6010</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,42 +6169,42 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
+          <t>2,41%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>9625</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>4788</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>17335</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>1,6%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
           <t>2,87%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>9625</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>5012</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>17036</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>1,6%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="W22" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>378024</t>
+          <t>376503</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>388956</t>
+          <t>388633</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>203652</t>
+          <t>204612</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,47 +6277,47 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
+          <t>97,59%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>552</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>593364</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>585654</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>598201</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>98,4%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>97,13%</t>
         </is>
       </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>552</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>593364</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>585953</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>597977</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>98,4%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>97,17%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>15523</t>
+          <t>16981</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4269</t>
+          <t>3333</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17387</t>
+          <t>18276</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>439214</t>
+          <t>437756</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>451537</t>
+          <t>451513</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>96,27%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>209817</t>
+          <t>209403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>652265</t>
+          <t>651376</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>665383</t>
+          <t>666319</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29656</t>
+          <t>29063</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56954</t>
+          <t>54709</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1001</t>
+          <t>997</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>9173</t>
+          <t>8400</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31615</t>
+          <t>31268</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>59712</t>
+          <t>59237</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1975281</t>
+          <t>1977526</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2002579</t>
+          <t>2003172</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1031376</t>
+          <t>1032149</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1039548</t>
+          <t>1039552</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3013073</t>
+          <t>3013548</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3041170</t>
+          <t>3041517</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,06%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2016 (tasa de respuesta: 98,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3215</t>
+          <t>3240</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>16357</t>
+          <t>15525</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6994</t>
+          <t>7151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5068</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18069</t>
+          <t>18818</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>162315</t>
+          <t>163147</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175457</t>
+          <t>175432</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98188</t>
+          <t>98031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,35%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265785</t>
+          <t>265036</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279112</t>
+          <t>278786</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,21%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3171</t>
+          <t>3185</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14882</t>
+          <t>15792</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3190</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>14098</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>251487</t>
+          <t>250577</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263198</t>
+          <t>263184</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99273</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>101274</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>352920</t>
+          <t>353545</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>364453</t>
+          <t>364497</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,0%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>5559</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>6018</t>
+          <t>4656</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>864</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6831</t>
+          <t>8632</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195123</t>
+          <t>195973</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,82%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116460</t>
+          <t>117822</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>317179</t>
+          <t>315378</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323149</t>
+          <t>323146</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -8408,97 +8408,97 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2018</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230418</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>232436</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>146239</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>148300</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>378694</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>380736</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8751,97 +8751,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,2%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1746</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>4,78%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1872</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>84532</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>86436</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34824</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36570</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>121134</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>123006</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5073</t>
+          <t>6086</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,62 +9129,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1011</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1899</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5715</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1011</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5080</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,96%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>183213</t>
+          <t>182200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>102098</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103997</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>287203</t>
+          <t>286568</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4895</t>
+          <t>4450</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>17096</t>
+          <t>16375</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>4997</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19528</t>
+          <t>18177</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>365634</t>
+          <t>366355</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>377835</t>
+          <t>378280</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>253803</t>
+          <t>255211</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>623410</t>
+          <t>624761</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>637022</t>
+          <t>637749</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,96%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,19%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1138</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10002</t>
+          <t>10893</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7587</t>
+          <t>7692</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2838</t>
+          <t>2971</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12801</t>
+          <t>13801</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>434771</t>
+          <t>433880</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>443642</t>
+          <t>443635</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,75%</t>
+          <t>99,74%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>244619</t>
+          <t>244514</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>684178</t>
+          <t>683178</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>694141</t>
+          <t>694008</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,57%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22488</t>
+          <t>22072</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>44608</t>
+          <t>45121</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,49 +10138,49 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>6210</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>2095</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>12883</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
           <t>1,14%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>6210</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>2921</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>13756</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
           <t>36</t>
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27679</t>
+          <t>27460</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>52044</t>
+          <t>51938</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1936628</t>
+          <t>1936115</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1958748</t>
+          <t>1959164</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,47 +10251,47 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>98,89%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1075</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1124004</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1117331</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1128119</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
           <t>98,86%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1075</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1124004</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1116458</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1127293</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,45%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,78%</t>
-        </is>
-      </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3059406</t>
+          <t>3059512</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3083771</t>
+          <t>3083990</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023</t>
+          <t>Población según si han bebido alguna vez para calmar los nervios o para evitar la resaca en 2023 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,97 +10702,97 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>1492</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>178023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>89622</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>269080</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11045,97 +11045,97 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2712</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>1526</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>2187</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>251744</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>115444</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>369239</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>—</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1619</t>
+          <t>1443</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7654</t>
+          <t>8720</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,82 +11403,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,71%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>1051</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3679</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>4960</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>2404</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>9749</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>1,8%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1051</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3492</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,87%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>4960</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>2246</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>9405</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>1,8%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,54%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>177532</t>
+          <t>176466</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183567</t>
+          <t>183743</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,82 +11516,82 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>89221</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>86593</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>90272</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>95,92%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>270498</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>265709</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>273054</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>98,2%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>96,46%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>99,13%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>123</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>89221</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>86780</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>90272</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,13%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>328</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>270498</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>266053</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>273212</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>98,2%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>96,59%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>660</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6676</t>
+          <t>6233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3306</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>775</t>
+          <t>1123</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7034</t>
+          <t>6957</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171502</t>
+          <t>171945</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177497</t>
+          <t>177518</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,63%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,7 +11879,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121039</t>
+          <t>121324</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -11894,7 +11894,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295490</t>
+          <t>295567</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301749</t>
+          <t>301401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,63%</t>
         </is>
       </c>
     </row>
@@ -12074,97 +12074,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1267</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>2046</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>5,13%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>4,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>23,83%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>440</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>2490</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,11%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>27,67%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2437</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,11%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29879</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6208</t>
+          <t>6537</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -12237,7 +12237,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>76,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12257,7 +12257,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37292</t>
+          <t>37239</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -12272,7 +12272,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>859</t>
+          <t>797</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7330</t>
+          <t>7518</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>552</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5825</t>
+          <t>6135</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2248</t>
+          <t>2201</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10324</t>
+          <t>10223</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157718</t>
+          <t>157530</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>164189</t>
+          <t>164251</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90595</t>
+          <t>90285</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95894</t>
+          <t>95868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,96%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,43%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>251144</t>
+          <t>251245</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>259220</t>
+          <t>259267</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>13381</t>
+          <t>14718</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12800,7 +12800,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>16412</t>
+          <t>17070</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12815,7 +12815,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3983</t>
+          <t>3973</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23611</t>
+          <t>22347</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12850,7 +12850,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>294549</t>
+          <t>293212</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>304874</t>
+          <t>305044</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,7 +12908,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383872</t>
+          <t>383214</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -12923,7 +12923,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>684603</t>
+          <t>685867</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>704231</t>
+          <t>704241</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>649</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7416</t>
+          <t>7455</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>658</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>8079</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>270121</t>
+          <t>270082</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>276877</t>
+          <t>276888</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>98438</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>369283</t>
+          <t>370515</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>376704</t>
+          <t>376717</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,7 +13301,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,86%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>11182</t>
+          <t>12648</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27422</t>
+          <t>27601</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,82 +13461,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>0,8%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>9252</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>3393</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>18061</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>28069</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>18427</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>39892</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>9252</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>3608</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>18783</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>28069</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>19245</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>40527</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1551949</t>
+          <t>1551770</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1568189</t>
+          <t>1566723</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,82 +13574,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,26%</t>
+          <t>98,25%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>99,2%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>1193</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1018130</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1009321</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1023989</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>99,1%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>98,24%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,67%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2578684</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2566861</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>2588326</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>98,92%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
           <t>99,29%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>1193</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1018130</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1008599</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1023774</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>98,17%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,65%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2578684</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>2566226</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2587508</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="W29" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P32C-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P32C-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1935</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13329</t>
+          <t>12317</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4055</t>
+          <t>5688</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1981</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13778</t>
+          <t>14934</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>132820</t>
+          <t>133832</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144214</t>
+          <t>144304</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,88%</t>
+          <t>91,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69421</t>
+          <t>67788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205847</t>
+          <t>204691</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>217651</t>
+          <t>217644</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12350</t>
+          <t>12204</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2833</t>
+          <t>2135</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>12961</t>
+          <t>12784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>216467</t>
+          <t>216613</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>226694</t>
+          <t>226772</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>288607</t>
+          <t>288784</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>298735</t>
+          <t>299433</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,29%</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5464</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5232</t>
+          <t>5198</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
     </row>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>188476</t>
+          <t>189559</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1602,7 +1602,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>275677</t>
+          <t>275711</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1977</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13776</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7164</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2972</t>
+          <t>3000</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15533</t>
+          <t>15994</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>224119</t>
+          <t>223948</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>235918</t>
+          <t>235513</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123762</t>
+          <t>123676</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>353289</t>
+          <t>352828</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>365850</t>
+          <t>365822</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4113</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2125,7 +2125,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2145,7 +2145,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7910</t>
+          <t>7479</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2160,7 +2160,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9488</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>92597</t>
+          <t>92785</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2233,7 +2233,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39386</t>
+          <t>39817</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2288,7 +2288,7 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>134706</t>
+          <t>135021</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
@@ -2303,7 +2303,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5159</t>
+          <t>5801</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>881</t>
+          <t>873</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7958</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>188237</t>
+          <t>187278</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,89%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>106624</t>
+          <t>105982</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>298109</t>
+          <t>298207</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>305186</t>
+          <t>305194</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3303</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>14652</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>274772</t>
+          <t>275024</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>285744</t>
+          <t>285733</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406128</t>
+          <t>405840</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>417147</t>
+          <t>416998</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3282</t>
+          <t>3262</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13348</t>
+          <t>13594</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1006</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7950</t>
+          <t>8392</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4722</t>
+          <t>4665</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>17674</t>
+          <t>16634</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>479540</t>
+          <t>479294</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>489606</t>
+          <t>489626</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>97,24%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,33%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>231988</t>
+          <t>231546</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239938</t>
+          <t>238932</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,58%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>715152</t>
+          <t>716192</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>728104</t>
+          <t>728161</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>25161</t>
+          <t>24416</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>49639</t>
+          <t>48743</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>17009</t>
+          <t>16168</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>31509</t>
+          <t>31482</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57626</t>
+          <t>57897</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1830279</t>
+          <t>1831175</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1854757</t>
+          <t>1855502</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>877575</t>
+          <t>878416</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>891114</t>
+          <t>890882</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,1%</t>
+          <t>98,19%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2716877</t>
+          <t>2716606</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2742994</t>
+          <t>2743021</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6260</t>
+          <t>6333</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19905</t>
+          <t>20425</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6012</t>
+          <t>5162</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6857</t>
+          <t>7208</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21280</t>
+          <t>21642</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>155420</t>
+          <t>154900</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169065</t>
+          <t>168992</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>103680</t>
+          <t>104530</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>263737</t>
+          <t>263375</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278160</t>
+          <t>277809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,53%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1786</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11378</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>1866</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11099</t>
+          <t>11671</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>297848</t>
+          <t>298191</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307440</t>
+          <t>307433</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>447499</t>
+          <t>446927</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>456793</t>
+          <t>456732</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,59%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9246</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9955</t>
+          <t>9173</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,35%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>177559</t>
+          <t>177175</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>185779</t>
+          <t>185785</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>264192</t>
+          <t>264974</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>273143</t>
+          <t>273151</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,64%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>915</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8799</t>
+          <t>8945</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>914</t>
+          <t>918</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9797</t>
+          <t>9261</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>119409</t>
+          <t>119263</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>127294</t>
+          <t>127293</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>172520</t>
+          <t>173056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>181403</t>
+          <t>181399</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5345</t>
+          <t>4568</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5791,7 +5791,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5846,7 +5846,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5355</t>
+          <t>5291</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5861,7 +5861,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179861</t>
+          <t>180638</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5899,7 +5899,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5954,7 +5954,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>274057</t>
+          <t>274121</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -5969,7 +5969,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4694</t>
+          <t>3937</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16824</t>
+          <t>15104</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5050</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4788</t>
+          <t>4765</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17335</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>376503</t>
+          <t>378223</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>388633</t>
+          <t>389390</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>204612</t>
+          <t>204119</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,36%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>585654</t>
+          <t>585672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>598201</t>
+          <t>598224</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3224</t>
+          <t>3249</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>16981</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6477,7 +6477,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6497,7 +6497,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5706</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6512,7 +6512,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3333</t>
+          <t>3359</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>18276</t>
+          <t>17909</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6547,7 +6547,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,67%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>437756</t>
+          <t>437610</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>451513</t>
+          <t>451488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,7 +6585,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,23%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>209403</t>
+          <t>209209</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -6620,7 +6620,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>651376</t>
+          <t>651743</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>666319</t>
+          <t>666293</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,7 +6655,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29063</t>
+          <t>30521</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>54709</t>
+          <t>56367</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,82 +6815,82 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>3038</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>992</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>8150</t>
+        </is>
+      </c>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>0,1%</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>43958</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>31979</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>58695</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>3038</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
-        <is>
-          <t>997</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr">
-        <is>
-          <t>8400</t>
-        </is>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>0,1%</t>
-        </is>
-      </c>
-      <c r="P28" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>43958</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>31268</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>59237</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,43%</t>
-        </is>
-      </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1977526</t>
+          <t>1975868</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2003172</t>
+          <t>2001714</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,82 +6928,82 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
+          <t>98,5%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>1037511</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>1032399</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>1039557</t>
+        </is>
+      </c>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>99,22%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,9%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2824</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>3028827</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>3014090</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>3040806</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
           <t>98,57%</t>
         </is>
       </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>953</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>1037511</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
-        <is>
-          <t>1032149</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>1039552</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,9%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>3028827</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>3013548</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>3041517</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,57%</t>
-        </is>
-      </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3240</t>
+          <t>3559</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>15525</t>
+          <t>16322</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5068</t>
+          <t>4717</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18818</t>
+          <t>18097</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,38%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163147</t>
+          <t>162350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>175432</t>
+          <t>175113</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,7 +7527,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98031</t>
+          <t>98673</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -7542,7 +7542,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>265036</t>
+          <t>265757</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278786</t>
+          <t>279137</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,62%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3185</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15792</t>
+          <t>15148</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3146</t>
+          <t>3276</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14098</t>
+          <t>14994</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>250577</t>
+          <t>251221</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>263184</t>
+          <t>263195</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,31%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353545</t>
+          <t>352649</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>364497</t>
+          <t>364367</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8085,7 +8085,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4656</t>
+          <t>5566</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8632</t>
+          <t>7785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8155,7 +8155,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>195973</t>
+          <t>195166</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8213,7 +8213,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117822</t>
+          <t>116912</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>315378</t>
+          <t>316225</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>323146</t>
+          <t>323144</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,7 +8263,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -9099,7 +9099,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6086</t>
+          <t>5889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5715</t>
+          <t>5092</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -9207,7 +9207,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182200</t>
+          <t>182397</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,77%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9277,7 +9277,7 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>286568</t>
+          <t>287191</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
@@ -9292,7 +9292,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4450</t>
+          <t>4395</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16375</t>
+          <t>17445</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9477,7 +9477,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4997</t>
+          <t>5020</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9492,7 +9492,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5189</t>
+          <t>5186</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>18353</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9527,7 +9527,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>366355</t>
+          <t>365285</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>378280</t>
+          <t>378335</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>255211</t>
+          <t>255188</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -9600,7 +9600,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>624761</t>
+          <t>624585</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>637749</t>
+          <t>637752</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,7 +9635,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1142</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10893</t>
+          <t>9856</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9800,7 +9800,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9820,7 +9820,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>7692</t>
+          <t>7577</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9835,7 +9835,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>2971</t>
+          <t>2215</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>13801</t>
+          <t>13766</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,7 +9865,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>433880</t>
+          <t>434917</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>443635</t>
+          <t>443631</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,7 +9908,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>244514</t>
+          <t>244629</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
@@ -9943,7 +9943,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,95%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>683178</t>
+          <t>683213</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>694008</t>
+          <t>694764</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9983,7 +9983,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,68%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>22072</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>45121</t>
+          <t>44470</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10163,7 +10163,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>12883</t>
+          <t>12297</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10178,7 +10178,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>27460</t>
+          <t>26676</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>51938</t>
+          <t>51967</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1936115</t>
+          <t>1936766</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1959164</t>
+          <t>1959032</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,7 +10271,7 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1117331</t>
+          <t>1117917</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
@@ -10286,7 +10286,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3059512</t>
+          <t>3059483</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3083990</t>
+          <t>3084774</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,14%</t>
         </is>
       </c>
     </row>
@@ -10810,7 +10810,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -10880,7 +10880,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>179889</t>
+          <t>169899</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90683</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>270572</t>
+          <t>267130</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11153,7 +11153,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -11188,7 +11188,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11223,7 +11223,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>381594</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>254456</t>
+          <t>258711</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>116970</t>
+          <t>122883</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>381594</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>381594</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>371426</t>
+          <t>381594</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3909</t>
+          <t>4615</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1443</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8720</t>
+          <t>9474</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,7 +11418,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1069</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -11428,12 +11428,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3679</t>
+          <t>3486</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -11443,7 +11443,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4960</t>
+          <t>5685</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2404</t>
+          <t>2453</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9749</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,79%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>181277</t>
+          <t>182698</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>176466</t>
+          <t>177839</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183743</t>
+          <t>185554</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,54%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,27 +11531,27 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>89221</t>
+          <t>88142</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>86593</t>
+          <t>85725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>270498</t>
+          <t>270838</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>265709</t>
+          <t>266056</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273054</t>
+          <t>274070</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>97,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,46%</t>
+          <t>96,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,11%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>185186</t>
+          <t>187313</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>90272</t>
+          <t>89211</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>276523</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2314</t>
+          <t>2355</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6233</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>902</t>
+          <t>979</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -11771,12 +11771,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3633</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -11786,7 +11786,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3334</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1123</t>
+          <t>1201</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6957</t>
+          <t>8203</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>175864</t>
+          <t>201081</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>171945</t>
+          <t>197186</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177518</t>
+          <t>202753</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,27 +11874,27 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>123443</t>
+          <t>137387</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>121324</t>
+          <t>134733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>299308</t>
+          <t>338468</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>295567</t>
+          <t>333599</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>301401</t>
+          <t>340601</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>99,02%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,65%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>178178</t>
+          <t>203436</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>178178</t>
+          <t>203436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>178178</t>
+          <t>203436</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>124345</t>
+          <t>138366</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>341802</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>341802</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>302524</t>
+          <t>341802</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12104,7 +12104,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
@@ -12114,12 +12114,12 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>2560</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
@@ -12129,7 +12129,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>440</t>
+          <t>469</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12149,12 +12149,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>2490</t>
+          <t>2472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12164,7 +12164,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,49%</t>
         </is>
       </c>
     </row>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -12217,27 +12217,27 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8143</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6537</t>
+          <t>8285</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>76,17%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -12252,27 +12252,27 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>39289</t>
+          <t>44513</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>37239</t>
+          <t>42510</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>94,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>31146</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8583</t>
+          <t>10845</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39729</t>
+          <t>44982</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2900</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>797</t>
+          <t>772</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2216</t>
+          <t>2231</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>552</t>
+          <t>546</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6135</t>
+          <t>6213</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,22 +12482,22 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>5245</t>
+          <t>5131</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2201</t>
+          <t>2181</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>10701</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>162019</t>
+          <t>160073</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157530</t>
+          <t>156184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>164251</t>
+          <t>162201</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,22%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>94204</t>
+          <t>95963</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>90285</t>
+          <t>91981</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>95868</t>
+          <t>97648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,73%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,27 +12595,27 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>256223</t>
+          <t>256036</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>251245</t>
+          <t>250466</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>259267</t>
+          <t>258986</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,09%</t>
+          <t>95,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>165048</t>
+          <t>162973</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>96420</t>
+          <t>98194</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>261468</t>
+          <t>261167</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6871</t>
+          <t>6995</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2860</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>14718</t>
+          <t>13610</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>4643</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1726</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>17070</t>
+          <t>16976</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>11514</t>
+          <t>13864</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3973</t>
+          <t>7207</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22347</t>
+          <t>25669</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>4,39%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>301059</t>
+          <t>342710</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>293212</t>
+          <t>336095</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>305044</t>
+          <t>346845</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>395641</t>
+          <t>228181</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>383214</t>
+          <t>218074</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>400284</t>
+          <t>233324</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>696700</t>
+          <t>570891</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>685867</t>
+          <t>559086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>704241</t>
+          <t>577548</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>307930</t>
+          <t>349705</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>400284</t>
+          <t>235050</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>400284</t>
+          <t>235050</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>400284</t>
+          <t>235050</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>708214</t>
+          <t>584755</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>708214</t>
+          <t>584755</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>708214</t>
+          <t>584755</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,22 +13098,22 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>718</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7455</t>
+          <t>8326</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
@@ -13123,7 +13123,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>2695</t>
+          <t>3018</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>8117</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,89%</t>
         </is>
       </c>
     </row>
@@ -13211,27 +13211,27 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>274842</t>
+          <t>311318</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>270082</t>
+          <t>306010</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>276888</t>
+          <t>313618</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>374667</t>
+          <t>426271</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>370515</t>
+          <t>421172</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>376717</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>100,0%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>277537</t>
+          <t>314336</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>277537</t>
+          <t>314336</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>277537</t>
+          <t>314336</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>99825</t>
+          <t>114954</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>377362</t>
+          <t>429289</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>18817</t>
+          <t>19884</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>12648</t>
+          <t>13181</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>27601</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,67 +13476,67 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>9252</t>
+          <t>11618</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3393</t>
+          <t>5046</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>18061</t>
+          <t>23533</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="R28" s="2" t="inlineStr">
+        <is>
+          <t>31502</t>
+        </is>
+      </c>
+      <c r="S28" s="2" t="inlineStr">
+        <is>
+          <t>21866</t>
+        </is>
+      </c>
+      <c r="T28" s="2" t="inlineStr">
+        <is>
+          <t>45461</t>
+        </is>
+      </c>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>1,22%</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
           <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q28" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="R28" s="2" t="inlineStr">
-        <is>
-          <t>28069</t>
-        </is>
-      </c>
-      <c r="S28" s="2" t="inlineStr">
-        <is>
-          <t>18427</t>
-        </is>
-      </c>
-      <c r="T28" s="2" t="inlineStr">
-        <is>
-          <t>39892</t>
-        </is>
-      </c>
-      <c r="U28" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="V28" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="W28" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1560554</t>
+          <t>1660625</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1551770</t>
+          <t>1651422</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1566723</t>
+          <t>1667328</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,67 +13589,67 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1018130</t>
+          <t>895115</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1009321</t>
+          <t>883200</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1023989</t>
+          <t>901687</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>98,72%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>99,44%</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr">
+        <is>
+          <t>2756</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>2555740</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>2541781</t>
+        </is>
+      </c>
+      <c r="T29" s="2" t="inlineStr">
+        <is>
+          <t>2565376</t>
+        </is>
+      </c>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
           <t>98,24%</t>
         </is>
       </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>99,67%</t>
-        </is>
-      </c>
-      <c r="Q29" s="2" t="inlineStr">
-        <is>
-          <t>2756</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr">
-        <is>
-          <t>2578684</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>2566861</t>
-        </is>
-      </c>
-      <c r="T29" s="2" t="inlineStr">
-        <is>
-          <t>2588326</t>
-        </is>
-      </c>
-      <c r="U29" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="V29" s="2" t="inlineStr">
-        <is>
-          <t>98,47%</t>
-        </is>
-      </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,15%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1579371</t>
+          <t>1680509</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1027382</t>
+          <t>906733</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>2606753</t>
+          <t>2587242</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
